--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488182_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488182_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3622</v>
+        <v>5.353</v>
       </c>
       <c r="E2" t="n">
-        <v>0.702</v>
+        <v>1.6928</v>
       </c>
       <c r="F2" t="n">
         <v>3.6602</v>
@@ -610,10 +610,10 @@
         <v>3.1499</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1751</v>
+        <v>-0.1844</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1279</v>
+        <v>-0.1371</v>
       </c>
       <c r="U2" t="n">
         <v>-0.0473</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RUIZ CORDAL</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5917</v>
+        <v>3.9673</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8525</v>
+        <v>1.2149</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7392</v>
+        <v>2.7524</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3854</v>
+        <v>2.2397</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7264</v>
+        <v>2.0984</v>
       </c>
       <c r="I3" t="n">
-        <v>0.659</v>
+        <v>0.1413</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1906</v>
+        <v>1.9694</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4855</v>
+        <v>1.7821</v>
       </c>
       <c r="L3" t="n">
-        <v>0.705</v>
+        <v>0.1872</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1949</v>
+        <v>0.2703</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2409</v>
+        <v>0.3163</v>
       </c>
       <c r="O3" t="n">
         <v>-0.046</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4087</v>
+        <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5904</v>
+        <v>0.8011</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9849</v>
+        <v>0.1719</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3944</v>
+        <v>0.6292</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>J. RUIZ CORDAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2193</v>
+        <v>3.723</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8116</v>
+        <v>2.4516</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4077</v>
+        <v>1.2714</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2397</v>
+        <v>2.3854</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0984</v>
+        <v>1.7264</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1413</v>
+        <v>0.659</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9694</v>
+        <v>2.1906</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7821</v>
+        <v>1.4855</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1872</v>
+        <v>0.705</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2703</v>
+        <v>0.1949</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3163</v>
+        <v>0.2409</v>
       </c>
       <c r="O4" t="n">
         <v>-0.046</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9264</v>
+        <v>1.4823</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8529</v>
+        <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0532</v>
+        <v>-0.4592</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2313</v>
+        <v>-0.3858</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2845</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0995</v>
+        <v>2.3604</v>
       </c>
       <c r="E5" t="n">
-        <v>1.017</v>
+        <v>1.4749</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0825</v>
+        <v>0.8855</v>
       </c>
       <c r="G5" t="n">
         <v>0.366</v>
@@ -844,13 +844,13 @@
         <v>2.9646</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1189</v>
+        <v>0.1421</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4203</v>
+        <v>0.0376</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3014</v>
+        <v>0.1044</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0005</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>I. GARCÍA REYES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2313</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3154</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9159</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1269</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3434</v>
+        <v>0.3221</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7834</v>
+        <v>0.6221</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1907</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.885</v>
+        <v>0.3221</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3057</v>
+        <v>0.6221</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0639</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4584</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5223</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6171</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2473</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6302</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. GARCÍA REYES</t>
+          <t>I. GARCIA REYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.4391</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.1101</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.1753</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3221</v>
+        <v>0.4916</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6221</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.492</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3221</v>
+        <v>0.1288</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6221</v>
+        <v>-0.6208</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.3167</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.3627</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.046</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.4756</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.0529</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.4228</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>M. PARRA JIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8263</v>
+        <v>0.6106</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0701</v>
+        <v>-0.451</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7562</v>
+        <v>1.0616</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4439</v>
+        <v>1.7752</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9999</v>
+        <v>0.3221</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.556</v>
+        <v>1.4531</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6637999999999999</v>
+        <v>1.4585</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1507</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.487</v>
+        <v>1.3686</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2198</v>
+        <v>0.3167</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1508</v>
+        <v>0.2322</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.4087</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.891</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5323</v>
+        <v>0.3177</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7796999999999999</v>
+        <v>-0.0566</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7526</v>
+        <v>0.3743</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7397</v>
+        <v>0.4711</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4236</v>
+        <v>0.0319</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3161</v>
+        <v>0.4392</v>
       </c>
       <c r="G10" t="n">
         <v>0.2447</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1244</v>
+        <v>-0.1443</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3793</v>
+        <v>-0.0124</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2549</v>
+        <v>-0.1318</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PARRA JIMENEZ</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2616</v>
+        <v>0.3772</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7015</v>
+        <v>-0.1574</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9631</v>
+        <v>0.5346</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7752</v>
+        <v>0.4439</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3221</v>
+        <v>0.9999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4531</v>
+        <v>-0.556</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4585</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08989999999999999</v>
+        <v>1.1507</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3686</v>
+        <v>-0.487</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3167</v>
+        <v>-0.2198</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2322</v>
+        <v>-0.1508</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4823</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8529</v>
+        <v>-3.891</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0313</v>
+        <v>1.0831</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3071</v>
+        <v>0.5521</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2758</v>
+        <v>0.531</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. GARCIA REYES</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1195</v>
+        <v>0.2586</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7444</v>
+        <v>-0.805</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8639</v>
+        <v>1.0637</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1753</v>
+        <v>-2.1269</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4916</v>
+        <v>-1.3434</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.7834</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.492</v>
+        <v>-2.1907</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1288</v>
+        <v>-0.885</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6208</v>
+        <v>-1.3057</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3167</v>
+        <v>0.0639</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3627</v>
+        <v>-0.4584</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.046</v>
+        <v>0.5223</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0759</v>
+        <v>-0.3556</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2524</v>
+        <v>0.1269</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1766</v>
+        <v>-0.4825</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1148</v>
+        <v>0.2446</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6508</v>
+        <v>-0.7194</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7656</v>
+        <v>0.9639</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4941</v>
+        <v>0.7822</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1555</v>
+        <v>0.177</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6496</v>
+        <v>0.6052</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2195</v>
+        <v>0.5036</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4683</v>
+        <v>0.4207</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2488</v>
+        <v>0.0829</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2745</v>
+        <v>0.2786</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6239</v>
+        <v>-0.2437</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8984</v>
+        <v>0.5223</v>
       </c>
       <c r="P13" t="n">
+        <v>-0.5558999999999999</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-1.1117</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-1.8529</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7205</v>
+        <v>0.3326</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4216</v>
+        <v>-0.1113</v>
       </c>
       <c r="U13" t="n">
-        <v>1.299</v>
+        <v>0.4439</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.099</v>
+        <v>-0.2923</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9152</v>
+        <v>-1.6393</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8162</v>
+        <v>1.347</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7822</v>
+        <v>-0.4941</v>
       </c>
       <c r="H14" t="n">
-        <v>0.177</v>
+        <v>0.1555</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6052</v>
+        <v>-0.6496</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5036</v>
+        <v>-0.2195</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4207</v>
+        <v>-0.4683</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0829</v>
+        <v>0.2488</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2786</v>
+        <v>-0.2745</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2437</v>
+        <v>0.6239</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5223</v>
+        <v>-0.8984</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1117</v>
+        <v>-1.8529</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0109</v>
+        <v>1.3135</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3071</v>
+        <v>0.4331</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2962</v>
+        <v>0.8804</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.4781</v>
+        <v>-1.6613</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3744</v>
+        <v>-0.7546</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1037</v>
+        <v>-0.9067</v>
       </c>
       <c r="G15" t="n">
         <v>-4.1242</v>
@@ -1624,13 +1624,13 @@
         <v>0.9264</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2977</v>
+        <v>-0.4809</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4303</v>
+        <v>0.0501</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.728</v>
+        <v>-0.531</v>
       </c>
       <c r="V15" t="n">
         <v>2.2027</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>17.49909999999999</v>
+        <v>18.5935</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3162</v>
+        <v>4.410599999999999</v>
       </c>
       <c r="F16" t="n">
         <v>14.1829</v>
@@ -1669,25 +1669,25 @@
         <v>8.252599999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4116</v>
+        <v>5.411600000000002</v>
       </c>
       <c r="I16" t="n">
         <v>2.841399999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>8.145499999999998</v>
+        <v>8.145500000000002</v>
       </c>
       <c r="K16" t="n">
-        <v>5.381900000000001</v>
+        <v>5.3819</v>
       </c>
       <c r="L16" t="n">
         <v>2.763500000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1074999999999999</v>
+        <v>0.1074999999999997</v>
       </c>
       <c r="N16" t="n">
-        <v>0.02960000000000007</v>
+        <v>0.02959999999999963</v>
       </c>
       <c r="O16" t="n">
         <v>0.0779999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>16.6759</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7473</v>
+        <v>2.8413</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3727999999999999</v>
+        <v>0.7214</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1201</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
         <v>4.72</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8001</v>
+        <v>2.3396</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4562</v>
+        <v>0.8479</v>
       </c>
       <c r="F17" t="n">
-        <v>1.344</v>
+        <v>1.4917</v>
       </c>
       <c r="G17" t="n">
         <v>0.9941</v>
@@ -1780,13 +1780,13 @@
         <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3057</v>
+        <v>0.2338</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2897</v>
+        <v>0.102</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0159</v>
+        <v>0.1318</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Á. LLAMAS JIMENEZ</t>
+          <t>I. PEREZ SAENZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9441000000000001</v>
+        <v>1.0596</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.314</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.6246</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3221</v>
+        <v>0.7782</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6221</v>
+        <v>-0.1536</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9441000000000001</v>
+        <v>1.0306</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3221</v>
+        <v>1.0306</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6221</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.406</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.2524</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.1536</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.1209</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.2851</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.1641</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. PEREZ SAENZ</t>
+          <t>Á. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7326</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6476</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6246</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7782</v>
+        <v>0.3221</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1536</v>
+        <v>0.6221</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0306</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0306</v>
+        <v>0.3221</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.6221</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.406</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2524</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1536</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4479</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0649</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>A. MARQUEZ MARQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7137</v>
+        <v>0.3865</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4639</v>
+        <v>0.844</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7502</v>
+        <v>-0.4575</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6179</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3528</v>
+        <v>-0.545</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9707</v>
+        <v>-0.2841</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2125</v>
+        <v>0.6551</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4554</v>
+        <v>0.5401</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7572</v>
+        <v>0.115</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8304</v>
+        <v>-1.4842</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1026</v>
+        <v>-1.0851</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7278</v>
+        <v>-0.3991</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
         <v>2.0382</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2199</v>
+        <v>-0.2285</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1779</v>
+        <v>-0.4759</v>
       </c>
       <c r="U20" t="n">
-        <v>0.042</v>
+        <v>0.2474</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MARQUEZ MARQUEZ</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3311</v>
+        <v>0.1668</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1585</v>
+        <v>0.6805</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4896</v>
+        <v>-0.5137</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.6179</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.545</v>
+        <v>0.3528</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2841</v>
+        <v>-0.9707</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6551</v>
+        <v>2.2125</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5401</v>
+        <v>1.4554</v>
       </c>
       <c r="L21" t="n">
-        <v>0.115</v>
+        <v>0.7572</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4842</v>
+        <v>-2.8304</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0851</v>
+        <v>-1.1026</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3991</v>
+        <v>-1.7278</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
         <v>2.0382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.327</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1614</v>
+        <v>-0.6056</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2153</v>
+        <v>0.2785</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5515</v>
+        <v>-0.3888</v>
       </c>
       <c r="E22" t="n">
         <v>-0.541</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0105</v>
+        <v>0.1522</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5194</v>
@@ -2170,13 +2170,13 @@
         <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7732</v>
+        <v>-0.6106</v>
       </c>
       <c r="T22" t="n">
         <v>-0.7113</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0619</v>
+        <v>0.1007</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>A. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5834</v>
+        <v>-1.1011</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.655</v>
+        <v>-1.109</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0716</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5561</v>
+        <v>-1.0961</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9893</v>
+        <v>-1.8303</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4332</v>
+        <v>0.7342</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4499</v>
+        <v>-0.125</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8385</v>
+        <v>-0.8206</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.6956</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8937</v>
+        <v>-0.9711</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1508</v>
+        <v>-1.0097</v>
       </c>
       <c r="O23" t="n">
-        <v>1.0446</v>
+        <v>0.0386</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.1499</v>
+        <v>-1.297</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7057</v>
+        <v>-2.7793</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1226</v>
+        <v>0.0326</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5006</v>
+        <v>-0.0929</v>
       </c>
       <c r="U23" t="n">
-        <v>0.622</v>
+        <v>0.1256</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2594</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. LLAMAS JIMENEZ</t>
+          <t>F. BENITEZ SIERRA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8187</v>
+        <v>-2.4714</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7945</v>
+        <v>-1.0462</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0242</v>
+        <v>-1.4253</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0961</v>
+        <v>-0.9823</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8303</v>
+        <v>0.0052</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7342</v>
+        <v>-0.9875</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.125</v>
+        <v>0.5051</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8206</v>
+        <v>0.4636</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6956</v>
+        <v>0.0415</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9711</v>
+        <v>-1.4874</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0097</v>
+        <v>-0.4584</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0386</v>
+        <v>-1.029</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.297</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6849</v>
+        <v>-0.5453</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7784</v>
+        <v>-0.6249</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0935</v>
+        <v>0.0796</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2594</v>
+        <v>-0.9439</v>
       </c>
       <c r="W24" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6289</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. BENITEZ SIERRA</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7315</v>
+        <v>-3.0574</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.242</v>
+        <v>-4.9074</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4894</v>
+        <v>1.85</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9823</v>
+        <v>-1.5561</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0052</v>
+        <v>-1.9893</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9875</v>
+        <v>0.4332</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5051</v>
+        <v>-2.4499</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4636</v>
+        <v>-1.8385</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0415</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4874</v>
+        <v>0.8937</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4584</v>
+        <v>-0.1508</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.029</v>
+        <v>1.0446</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8053</v>
+        <v>1.6486</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8207</v>
+        <v>1.2482</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0154</v>
+        <v>0.4004</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.7586</v>
+        <v>-4.5073</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.3752</v>
+        <v>-3.5918</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3834</v>
+        <v>-0.9155</v>
       </c>
       <c r="G26" t="n">
         <v>-3.3412</v>
@@ -2482,13 +2482,13 @@
         <v>1.8529</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1406</v>
+        <v>0.1107</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7784</v>
+        <v>0.005</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3621</v>
+        <v>0.1057</v>
       </c>
       <c r="V26" t="n">
         <v>-2.2033</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.914999999999999</v>
+        <v>-9.564</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.2455</v>
+        <v>-7.0496</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.6695</v>
+        <v>-2.5143</v>
       </c>
       <c r="G27" t="n">
         <v>-1.8736</v>
@@ -2560,13 +2560,13 @@
         <v>1.6676</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.9859</v>
+        <v>-0.6348</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8754</v>
+        <v>-0.6796</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1104</v>
+        <v>0.0448</v>
       </c>
       <c r="V27" t="n">
         <v>-4.091</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-17.4993</v>
+        <v>-16.1934</v>
       </c>
       <c r="E28" t="n">
-        <v>-14.1829</v>
+        <v>-14.183</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.3162</v>
+        <v>-2.0105</v>
       </c>
       <c r="G28" t="n">
         <v>-8.2529</v>
@@ -2611,13 +2611,13 @@
         <v>-2.8413</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.107599999999999</v>
+        <v>-0.1075999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.02959999999999982</v>
+        <v>-0.02959999999999938</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.07780000000000009</v>
+        <v>-0.07780000000000031</v>
       </c>
       <c r="M28" t="n">
         <v>-8.1454</v>
@@ -2626,7 +2626,7 @@
         <v>-5.3819</v>
       </c>
       <c r="O28" t="n">
-        <v>-2.7634</v>
+        <v>-2.763399999999999</v>
       </c>
       <c r="P28" t="n">
         <v>-2.7794</v>
@@ -2638,13 +2638,13 @@
         <v>13.8967</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.7471</v>
+        <v>-0.4413999999999998</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.1198</v>
+        <v>-2.1201</v>
       </c>
       <c r="U28" t="n">
-        <v>0.3730000000000001</v>
+        <v>1.6786</v>
       </c>
       <c r="V28" t="n">
         <v>-4.7199</v>
